--- a/data/trans_orig/P1434-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,19 +526,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2007</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -733,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58365</t>
+          <t>60107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91085</t>
+          <t>92360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +688,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73389</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>73389</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>58365</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>91085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>940638</t>
+          <t>939363</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>973358</t>
+          <t>971616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +766,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>959</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>958334</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>939363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>958334</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>940638</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>973358</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>94,34%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -984,70 +854,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1031723</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1031723</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1031723</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1076,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +926,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>20985</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>13535</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>31965</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1661448</t>
+          <t>1663108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1679878</t>
+          <t>1680439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1004,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1672428</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1663108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1680439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1627</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1672428</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1661448</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1679878</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1327,70 +1092,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1693413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1693413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1693413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1649</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1693413</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1693413</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1693413</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1419,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1164,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>11814</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>20991</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530417</t>
+          <t>530493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545295</t>
+          <t>545677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1242,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>517</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539594</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>545677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>539594</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>530417</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>545295</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1670,70 +1330,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>527</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>551408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>551408</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>551408</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>551408</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1762,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86256</t>
+          <t>86266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125642</t>
+          <t>127218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,77 +1407,42 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>106188</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>86256</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>125642</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3150901</t>
+          <t>3149325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190287</t>
+          <t>3190277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1480,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1900,70 +1490,35 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3170355</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3149325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3190277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3170355</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3150901</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3190287</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>97,37%</t>
         </is>
@@ -2013,70 +1568,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3214</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2090,13 +1610,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2110,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2129,19 +1648,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2012</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2158,7 +1670,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2167,17 +1679,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2248,41 +1749,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2305,13 +1771,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2336,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92812</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,82 +1810,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73873</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>73873</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>58592</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>92812</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>879639</t>
+          <t>879824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>913859</t>
+          <t>914735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,82 +1888,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>840</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>898578</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>898578</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>879639</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>913859</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -2587,70 +1976,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>907</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>972451</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>972451</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>972451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>972451</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>972451</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>972451</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2679,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2048,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2704,70 +2058,35 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>40010</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>28049</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>54344</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
@@ -2792,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909613</t>
+          <t>1909459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1935908</t>
+          <t>1934540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,77 +2131,42 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1923947</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1909459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1934540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1923947</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1909613</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1935908</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2930,70 +2214,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1963957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1963957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1963957</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1963957</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1963957</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1963957</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3022,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,77 +2291,42 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>10526</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22395</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458786</t>
+          <t>459339</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476998</t>
+          <t>476988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +2364,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3160,70 +2374,35 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470655</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>470655</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>458786</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>476998</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>99,13%</t>
         </is>
@@ -3273,70 +2452,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481181</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481181</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>481181</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>481181</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>481181</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3365,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104588</t>
+          <t>102601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147440</t>
+          <t>148800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,82 +2524,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>124409</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>104588</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>147440</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270150</t>
+          <t>3268790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3313002</t>
+          <t>3314989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,82 +2602,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3293181</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3268790</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3314989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3293181</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3270150</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3313002</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3616,70 +2690,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3417590</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3417590</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3417590</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3417590</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3417590</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3417590</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3693,13 +2732,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3713,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3732,19 +2770,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2016</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3761,7 +2792,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3770,17 +2801,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3851,41 +2871,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3908,13 +2893,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3939,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>49418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75976</t>
+          <t>77896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,82 +2932,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61600</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49418</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77896</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>61600</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>48990</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>75976</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678371</t>
+          <t>676451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>705357</t>
+          <t>704929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,82 +3010,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>693</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>676451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>704929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>692747</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>678371</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>705357</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>89,93%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -4190,70 +3098,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>762</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754347</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754347</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>754347</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>754347</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>754347</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4282,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55941</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,82 +3170,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>39615</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>55941</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2020444</t>
+          <t>2020806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2047515</t>
+          <t>2047832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,82 +3248,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2036770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2020806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2047832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2036770</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2020444</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2047515</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -4533,70 +3336,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2076385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2076385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2076385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2076385</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>2076385</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2076385</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4625,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,82 +3408,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>7787</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530397</t>
+          <t>531469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543379</t>
+          <t>543944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,82 +3486,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>494</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539099</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>531469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>539099</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>530397</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>543379</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4876,70 +3574,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546886</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>546886</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>546886</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>546886</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4968,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90763</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130969</t>
+          <t>130195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,82 +3646,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>109002</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>90763</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>130969</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3246649</t>
+          <t>3247423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3286855</t>
+          <t>3286494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,82 +3724,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3268616</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3247423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3286494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3268616</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3246649</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3286855</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -5219,70 +3812,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3377618</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3377618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3377618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3377618</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3377618</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3377618</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5296,13 +3854,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -5316,7 +3873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5335,19 +3892,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2023</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5364,7 +3914,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5373,17 +3923,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5454,41 +3993,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5511,13 +4015,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5542,12 +4039,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59310</t>
+          <t>59964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84117</t>
+          <t>86704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,82 +4054,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71634</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>71634</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>59310</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>84117</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +4117,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427469</t>
+          <t>424882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452276</t>
+          <t>451622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,82 +4132,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>569</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439952</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>439952</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>427469</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>452276</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -5793,70 +4220,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>688</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511586</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>511586</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>511586</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>511586</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5885,12 +4277,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97225</t>
+          <t>97105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,82 +4292,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>78045</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>55450</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>97225</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +4355,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2181428</t>
+          <t>2181548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2223203</t>
+          <t>2227182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,82 +4370,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2200608</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2181548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2227182</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2200608</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2181428</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2223203</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -6136,70 +4458,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2278653</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2278653</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2278653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2278653</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>2278653</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2278653</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6228,12 +4515,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,82 +4530,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29926</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>29926</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>22456</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>41076</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +4593,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600768</t>
+          <t>601173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619388</t>
+          <t>620586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,82 +4608,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611918</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>601173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>611918</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>600768</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>619388</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,6%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -6479,70 +4696,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>676</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>641844</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>641844</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>641844</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6571,12 +4753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138309</t>
+          <t>139074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205906</t>
+          <t>206874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,82 +4768,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>277</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179605</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>179605</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>138309</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>205906</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +4831,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3226177</t>
+          <t>3225209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3293774</t>
+          <t>3293009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,82 +4846,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3252478</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3225209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3293009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3070</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3252478</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3226177</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3293774</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -6822,70 +4934,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3432083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3432083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3432083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3347</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>3432083</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>3432083</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>3432083</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6899,13 +4976,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P1434-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92360</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>58327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92360</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939363</t>
+          <t>941474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>971616</t>
+          <t>973396</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>939363</t>
+          <t>941474</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>971616</t>
+          <t>973396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30447</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1663108</t>
+          <t>1662966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1680439</t>
+          <t>1680119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1663108</t>
+          <t>1662966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1680439</t>
+          <t>1680119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530493</t>
+          <t>530651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545677</t>
+          <t>545620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530493</t>
+          <t>530651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545677</t>
+          <t>545620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57716</t>
+          <t>55507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92627</t>
+          <t>91053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57716</t>
+          <t>55507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92627</t>
+          <t>91053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>879824</t>
+          <t>881398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>914735</t>
+          <t>916944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>879824</t>
+          <t>881398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>914735</t>
+          <t>916944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909459</t>
+          <t>1910793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1934540</t>
+          <t>1935461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1909459</t>
+          <t>1910793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1934540</t>
+          <t>1935461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21842</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459339</t>
+          <t>459150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476988</t>
+          <t>477000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459339</t>
+          <t>459150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>476988</t>
+          <t>477000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102601</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148800</t>
+          <t>148839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102601</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148800</t>
+          <t>148839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3268790</t>
+          <t>3268751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3314989</t>
+          <t>3315322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3268790</t>
+          <t>3268751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3314989</t>
+          <t>3315322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>48678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77896</t>
+          <t>77100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>48678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77896</t>
+          <t>77100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676451</t>
+          <t>677247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>704929</t>
+          <t>705669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676451</t>
+          <t>677247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>704929</t>
+          <t>705669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55579</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55579</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2020806</t>
+          <t>2021871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2047832</t>
+          <t>2047282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2020806</t>
+          <t>2021871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2047832</t>
+          <t>2047282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531469</t>
+          <t>530639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543944</t>
+          <t>543482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531469</t>
+          <t>530639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>543944</t>
+          <t>543482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91124</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130195</t>
+          <t>132098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91124</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130195</t>
+          <t>132098</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3247423</t>
+          <t>3245520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3286494</t>
+          <t>3287457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3247423</t>
+          <t>3245520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3286494</t>
+          <t>3287457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -4034,32 +4034,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>75754</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59964</t>
+          <t>62716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86704</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4069,32 +4069,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>75754</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59964</t>
+          <t>62716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86704</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -4112,32 +4112,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>439952</t>
+          <t>499315</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424882</t>
+          <t>483442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451622</t>
+          <t>512353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4147,32 +4147,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>439952</t>
+          <t>499315</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424882</t>
+          <t>483442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451622</t>
+          <t>512353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -4190,17 +4190,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4225,17 +4225,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>511586</t>
+          <t>575069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,32 +4272,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78045</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4307,32 +4307,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78045</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2200608</t>
+          <t>2134508</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2181548</t>
+          <t>2118150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2227182</t>
+          <t>2149585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2200608</t>
+          <t>2134508</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2181548</t>
+          <t>2118150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2227182</t>
+          <t>2149585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2278653</t>
+          <t>2218504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4510,32 +4510,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4545,32 +4545,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>24456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -4588,32 +4588,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>611918</t>
+          <t>673891</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601173</t>
+          <t>661289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620586</t>
+          <t>682152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4623,32 +4623,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>611918</t>
+          <t>673891</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>601173</t>
+          <t>661289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>620586</t>
+          <t>682152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>641844</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4748,32 +4748,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>179605</t>
+          <t>192467</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139074</t>
+          <t>169192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206874</t>
+          <t>215494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4783,32 +4783,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>179605</t>
+          <t>192467</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139074</t>
+          <t>169192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206874</t>
+          <t>215494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3252478</t>
+          <t>3307714</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3225209</t>
+          <t>3284687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3293009</t>
+          <t>3330989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,32 +4861,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3252478</t>
+          <t>3307714</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3225209</t>
+          <t>3284687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3293009</t>
+          <t>3330989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4904,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4939,17 +4939,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3432083</t>
+          <t>3500181</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
